--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>M_TimeGuard</t>
+          <t>M_SHEEP</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>M_SHEEP</t>
+          <t>M_TimeGuard</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -172,9 +172,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -639,6 +637,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -954,6 +953,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1700,6 +1700,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2756,7 +2757,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>M_TimeGuard</t>
+          <t>M_SHEEP</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
@@ -2829,6 +2830,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3184,6 +3186,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3354,27 +3357,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>SheetName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>TableName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>AdapterVersion</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>OutputCsv</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>SortKey</t>
         </is>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -637,7 +637,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -706,7 +705,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Level00</t>
+          <t>SC01</t>
         </is>
       </c>
       <c r="D4" s="20" t="n">
@@ -755,7 +754,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Level00</t>
+          <t>SC02</t>
         </is>
       </c>
       <c r="D5" s="23" t="n">
@@ -804,7 +803,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Level00</t>
+          <t>SC03</t>
         </is>
       </c>
       <c r="D6" s="23" t="n">
@@ -853,7 +852,7 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>Level00</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="D7" s="26" t="n">
@@ -953,7 +952,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1700,7 +1698,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2830,7 +2827,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3186,7 +3182,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblEncounterWaves" displayName="tblEncounterWaves" ref="A3:L25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblEncounterWaves" displayName="tblEncounterWaves" ref="A3:L27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="12">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="EncounterId"/>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="20" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M4" s="20" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M5" s="23" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M6" s="23" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="M8" s="23" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.38000106811523" customWidth="1" min="1" max="1"/>
@@ -1778,15 +1778,15 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="20" t="str"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>true</t>
@@ -1794,11 +1794,11 @@
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K4" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -1824,15 +1824,15 @@
         <v>10</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="23" t="str"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1840,11 +1840,11 @@
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K5" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
@@ -1870,15 +1870,15 @@
         <v>20</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="23" t="str"/>
+      <c r="H6" s="23"/>
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K6" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
@@ -1916,15 +1916,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="23" t="str"/>
+      <c r="H7" s="23"/>
       <c r="I7" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1932,11 +1932,11 @@
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K7" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
@@ -1962,15 +1962,15 @@
         <v>10</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="23" t="str"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1978,11 +1978,11 @@
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K8" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
@@ -2008,15 +2008,15 @@
         <v>20</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="23" t="str"/>
+      <c r="H9" s="23"/>
       <c r="I9" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K9" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
@@ -2054,15 +2054,15 @@
         <v>0</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="23" t="str"/>
+        <v>4</v>
+      </c>
+      <c r="H10" s="23"/>
       <c r="I10" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K10" s="23" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2100,31 +2100,31 @@
         <v>10</v>
       </c>
       <c r="E11" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>企微怪物表</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="23" t="str"/>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>刷怪规则</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>4</v>
-      </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2146,15 +2146,15 @@
         <v>20</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="23" t="str"/>
+        <v>4</v>
+      </c>
+      <c r="H12" s="23"/>
       <c r="I12" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2162,15 +2162,15 @@
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K12" s="23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2192,15 +2192,15 @@
         <v>0</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="23" t="str"/>
+        <v>4</v>
+      </c>
+      <c r="H13" s="23"/>
       <c r="I13" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2208,15 +2208,15 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K13" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2238,15 +2238,15 @@
         <v>10</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="23" t="str"/>
+        <v>5</v>
+      </c>
+      <c r="H14" s="23"/>
       <c r="I14" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K14" s="23" t="n">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2284,15 +2284,15 @@
         <v>20</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="23" t="str"/>
+        <v>4</v>
+      </c>
+      <c r="H15" s="23"/>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2300,15 +2300,15 @@
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K15" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2330,31 +2330,31 @@
         <v>0</v>
       </c>
       <c r="E16" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>企微怪物表</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="23" t="str"/>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>刷怪规则</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2376,15 +2376,15 @@
         <v>10</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="23" t="str"/>
+        <v>5</v>
+      </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2392,15 +2392,15 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K17" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
         <v>20</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="23" t="str"/>
+        <v>4</v>
+      </c>
+      <c r="H18" s="23"/>
       <c r="I18" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K18" s="23" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2468,15 +2468,15 @@
         <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="23" t="str"/>
+      <c r="H19" s="23"/>
       <c r="I19" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2484,15 +2484,15 @@
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K19" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2514,15 +2514,15 @@
         <v>10</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="23" t="str"/>
+        <v>7</v>
+      </c>
+      <c r="H20" s="23"/>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2530,15 +2530,15 @@
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K20" s="23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2560,15 +2560,15 @@
         <v>20</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="23" t="str"/>
+        <v>7</v>
+      </c>
+      <c r="H21" s="23"/>
       <c r="I21" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2576,15 +2576,15 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K21" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2606,15 +2606,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="23" t="str"/>
+        <v>7</v>
+      </c>
+      <c r="H22" s="23"/>
       <c r="I22" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2622,15 +2622,15 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K22" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L22" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2652,15 +2652,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="23" t="str"/>
+        <v>8</v>
+      </c>
+      <c r="H23" s="23"/>
       <c r="I23" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2668,15 +2668,15 @@
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K23" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2698,15 +2698,15 @@
         <v>20</v>
       </c>
       <c r="E24" s="23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="23" t="str"/>
+        <v>8</v>
+      </c>
+      <c r="H24" s="23"/>
       <c r="I24" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2714,15 +2714,15 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K24" s="23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L24" s="24" t="inlineStr">
         <is>
-          <t>按外部XLSX波次数量</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
@@ -2744,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
@@ -2764,15 +2764,107 @@
       </c>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
+          <t>企微怪物表</t>
         </is>
       </c>
       <c r="K25" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>Boss在0秒刷新；16近战/8远程/5精英援军</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Encounter.8.Wave.2</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="L25" s="27" t="inlineStr">
-        <is>
-          <t>Boss在0秒刷新</t>
+      <c r="G26" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>企微怪物表</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>Boss关增援波</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Encounter.8.Wave.3</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>企微怪物表</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="27" t="inlineStr">
+        <is>
+          <t>Boss关增援波</t>
         </is>
       </c>
     </row>
@@ -2782,10 +2874,10 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B4:B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+    <dataValidation sqref="B4:B27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblEncounters[Id]")</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+    <dataValidation sqref="I4:I27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -363,7 +363,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblSpawnProfiles" displayName="tblSpawnProfiles" ref="A3:M7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblSpawnProfiles" displayName="tblSpawnProfiles" ref="A3:M8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="EnemyRole"/>
@@ -2889,12 +2889,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.5" customWidth="1" min="1" max="1"/>
@@ -3214,31 +3214,88 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Spawn.Boss</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>M_SHEEP</t>
+        </is>
+      </c>
+      <c r="D8" s="26">
+        <v>700</v>
+      </c>
+      <c r="E8" s="26">
+        <v>950</v>
+      </c>
+      <c r="F8" s="26">
+        <v>220</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>NormalAroundAnchor</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Explicit</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>刷怪规则</t>
+        </is>
+      </c>
+      <c r="L8" s="26">
+        <v>13</v>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t>Boss使用双锚动态出生；不再使用固定坐标</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="B4:B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
-      <formula1>"Melee,Ranged,Elite,BossReinforcement"</formula1>
+    <dataValidation sqref="B4:B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+      <formula1>"Melee,Ranged,Elite,BossReinforcement,Boss"</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
-      <formula1>"M_SLIME,M_RABBIT,M_FOX,M_TimeGuard"</formula1>
+    <dataValidation sqref="C4:C8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+      <formula1>"M_SLIME,M_RABBIT,M_FOX,M_TimeGuard,M_SHEEP"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+    <dataValidation sqref="H4:H8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"NormalAroundAnchor"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+    <dataValidation sqref="I4:I8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"Explicit,UseEnemyRole"</formula1>
     </dataValidation>
-    <dataValidation sqref="J4:J7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
+    <dataValidation sqref="J4:J8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1786,7 +1786,7 @@
       <c r="G4" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="20"/>
+      <c r="H4" s="20" t="n"/>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>true</t>
@@ -1832,7 +1832,7 @@
       <c r="G5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="23"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1878,7 +1878,7 @@
       <c r="G6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="23" t="n"/>
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1924,7 +1924,7 @@
       <c r="G7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="23" t="n"/>
       <c r="I7" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1970,7 +1970,7 @@
       <c r="G8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="23" t="n"/>
       <c r="I8" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2016,7 +2016,7 @@
       <c r="G9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="23" t="n"/>
       <c r="I9" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2062,7 +2062,7 @@
       <c r="G10" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2108,7 +2108,7 @@
       <c r="G11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="23"/>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2154,7 +2154,7 @@
       <c r="G12" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="23"/>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2200,7 +2200,7 @@
       <c r="G13" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="23"/>
+      <c r="H13" s="23" t="n"/>
       <c r="I13" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2246,7 +2246,7 @@
       <c r="G14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="23"/>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2292,7 +2292,7 @@
       <c r="G15" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2338,7 +2338,7 @@
       <c r="G16" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="23"/>
+      <c r="H16" s="23" t="n"/>
       <c r="I16" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2384,7 +2384,7 @@
       <c r="G17" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="23"/>
+      <c r="H17" s="23" t="n"/>
       <c r="I17" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2430,7 +2430,7 @@
       <c r="G18" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="23"/>
+      <c r="H18" s="23" t="n"/>
       <c r="I18" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2476,7 +2476,7 @@
       <c r="G19" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="n"/>
       <c r="I19" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2522,7 +2522,7 @@
       <c r="G20" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H20" s="23"/>
+      <c r="H20" s="23" t="n"/>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2568,7 +2568,7 @@
       <c r="G21" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="23"/>
+      <c r="H21" s="23" t="n"/>
       <c r="I21" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2614,7 +2614,7 @@
       <c r="G22" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="23"/>
+      <c r="H22" s="23" t="n"/>
       <c r="I22" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2660,7 +2660,7 @@
       <c r="G23" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H23" s="23"/>
+      <c r="H23" s="23" t="n"/>
       <c r="I23" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2706,7 +2706,7 @@
       <c r="G24" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="23"/>
+      <c r="H24" s="23" t="n"/>
       <c r="I24" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2744,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="L25" s="27" t="inlineStr">
         <is>
-          <t>Boss在0秒刷新；16近战/8远程/5精英援军</t>
+          <t>Boss在0秒刷新；10近战/6远程/4精英援军（对齐第一关战斗1）</t>
         </is>
       </c>
     </row>
@@ -2794,15 +2794,15 @@
         <v>10</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" s="26"/>
+        <v>5</v>
+      </c>
+      <c r="H26" s="26" t="n"/>
       <c r="I26" s="26" t="inlineStr">
         <is>
           <t>true</t>
@@ -2840,15 +2840,15 @@
         <v>20</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="H27" s="26" t="n"/>
       <c r="I27" s="26" t="inlineStr">
         <is>
           <t>true</t>
@@ -2889,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3230,16 +3230,16 @@
           <t>M_SHEEP</t>
         </is>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="26" t="n">
         <v>950</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="26" t="n">
         <v>220</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="26" t="n">
         <v>0.9</v>
       </c>
       <c r="H8" s="26" t="inlineStr">
@@ -3262,7 +3262,7 @@
           <t>刷怪规则</t>
         </is>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="26" t="n">
         <v>13</v>
       </c>
       <c r="M8" s="27" t="inlineStr">
@@ -3295,7 +3295,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1781,7 +1781,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>0</v>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="M6" s="23" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="M8" s="23" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       <c r="G4" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="20"/>
+      <c r="H4" s="20" t="n"/>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>true</t>
@@ -1832,7 +1832,7 @@
       <c r="G5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="23"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1878,7 +1878,7 @@
       <c r="G6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="23" t="n"/>
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1924,7 +1924,7 @@
       <c r="G7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="23"/>
+      <c r="H7" s="23" t="n"/>
       <c r="I7" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -1970,7 +1970,7 @@
       <c r="G8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="23" t="n"/>
       <c r="I8" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2016,7 +2016,7 @@
       <c r="G9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="23" t="n"/>
       <c r="I9" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2054,15 +2054,15 @@
         <v>0</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F10" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2100,15 +2100,15 @@
         <v>10</v>
       </c>
       <c r="E11" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>6</v>
-      </c>
       <c r="G11" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2146,15 +2146,15 @@
         <v>20</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2192,15 +2192,15 @@
         <v>0</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F13" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="23"/>
+      <c r="H13" s="23" t="n"/>
       <c r="I13" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2238,15 +2238,15 @@
         <v>10</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2284,15 +2284,15 @@
         <v>20</v>
       </c>
       <c r="E15" s="23" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2330,15 +2330,15 @@
         <v>0</v>
       </c>
       <c r="E16" s="23" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="H16" s="23" t="n"/>
       <c r="I16" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2376,15 +2376,15 @@
         <v>10</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="H17" s="23" t="n"/>
       <c r="I17" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2422,15 +2422,15 @@
         <v>20</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="H18" s="23" t="n"/>
       <c r="I18" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2468,15 +2468,15 @@
         <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="H19" s="23" t="n"/>
       <c r="I19" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2514,15 +2514,15 @@
         <v>10</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="H20" s="23" t="n"/>
       <c r="I20" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2560,15 +2560,15 @@
         <v>20</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="H21" s="23" t="n"/>
       <c r="I21" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2606,15 +2606,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H22" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="H22" s="23" t="n"/>
       <c r="I22" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2652,15 +2652,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H23" s="23"/>
+        <v>16</v>
+      </c>
+      <c r="H23" s="23" t="n"/>
       <c r="I23" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2698,15 +2698,15 @@
         <v>20</v>
       </c>
       <c r="E24" s="23" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" s="23"/>
+        <v>16</v>
+      </c>
+      <c r="H24" s="23" t="n"/>
       <c r="I24" s="23" t="inlineStr">
         <is>
           <t>true</t>
@@ -2744,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F25" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="26" t="n">
-        <v>8</v>
-      </c>
       <c r="G25" s="26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
@@ -2794,15 +2794,15 @@
         <v>10</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="H26" s="26" t="n"/>
       <c r="I26" s="26" t="inlineStr">
         <is>
           <t>true</t>
@@ -2840,15 +2840,15 @@
         <v>20</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="H27" s="26" t="n"/>
       <c r="I27" s="26" t="inlineStr">
         <is>
           <t>true</t>
@@ -2889,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3230,16 +3230,16 @@
           <t>M_SHEEP</t>
         </is>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="26" t="n">
         <v>950</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="26" t="n">
         <v>220</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="26" t="n">
         <v>0.9</v>
       </c>
       <c r="H8" s="26" t="inlineStr">
@@ -3262,7 +3262,7 @@
           <t>刷怪规则</t>
         </is>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="26" t="n">
         <v>13</v>
       </c>
       <c r="M8" s="27" t="inlineStr">
@@ -3295,7 +3295,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1781,7 +1781,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>0</v>
@@ -2011,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="inlineStr">
@@ -2106,7 +2106,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H11" s="23" t="n"/>
       <c r="I11" s="23" t="inlineStr">
@@ -2152,7 +2152,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H12" s="23" t="n"/>
       <c r="I12" s="23" t="inlineStr">
@@ -2198,7 +2198,7 @@
         <v>16</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H13" s="23" t="n"/>
       <c r="I13" s="23" t="inlineStr">
@@ -2244,7 +2244,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H14" s="23" t="n"/>
       <c r="I14" s="23" t="inlineStr">
@@ -2290,7 +2290,7 @@
         <v>22</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="23" t="n"/>
       <c r="I15" s="23" t="inlineStr">
@@ -2336,7 +2336,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="23" t="n"/>
       <c r="I16" s="23" t="inlineStr">
@@ -2382,7 +2382,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H17" s="23" t="n"/>
       <c r="I17" s="23" t="inlineStr">
@@ -2428,7 +2428,7 @@
         <v>22</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="23" t="n"/>
       <c r="I18" s="23" t="inlineStr">
@@ -2474,7 +2474,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H19" s="23" t="n"/>
       <c r="I19" s="23" t="inlineStr">
@@ -2520,7 +2520,7 @@
         <v>18</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H20" s="23" t="n"/>
       <c r="I20" s="23" t="inlineStr">
@@ -2566,7 +2566,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H21" s="23" t="n"/>
       <c r="I21" s="23" t="inlineStr">
@@ -2612,7 +2612,7 @@
         <v>22</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H22" s="23" t="n"/>
       <c r="I22" s="23" t="inlineStr">
@@ -2658,7 +2658,7 @@
         <v>18</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H23" s="23" t="n"/>
       <c r="I23" s="23" t="inlineStr">
@@ -2704,7 +2704,7 @@
         <v>26</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H24" s="23" t="n"/>
       <c r="I24" s="23" t="inlineStr">
@@ -2750,7 +2750,7 @@
         <v>16</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>18</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H26" s="26" t="n"/>
       <c r="I26" s="26" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>22</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H27" s="26" t="n"/>
       <c r="I27" s="26" t="inlineStr">

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -2057,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>6</v>
@@ -2103,7 +2103,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>7</v>
@@ -2149,7 +2149,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>6</v>
@@ -2195,7 +2195,7 @@
         <v>28</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>6</v>
@@ -2241,7 +2241,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>7</v>
@@ -2287,7 +2287,7 @@
         <v>36</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>6</v>
@@ -2333,7 +2333,7 @@
         <v>32</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>6</v>
@@ -2379,7 +2379,7 @@
         <v>24</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>7</v>
@@ -2425,7 +2425,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>7</v>
@@ -2517,7 +2517,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
         <v>44</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>10</v>
@@ -2609,7 +2609,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>30</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>12</v>
@@ -2701,7 +2701,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>12</v>
@@ -2747,7 +2747,7 @@
         <v>32</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G25" s="26" t="n">
         <v>7</v>
@@ -2797,7 +2797,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G26" s="26" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>36</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>10</v>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1047,592 +1047,592 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>Encounter.1</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
+          <t xml:space="preserve">Encounter.1</t>
+        </is>
+      </c>
+      <c r="B4" s="20">
         <v>1</v>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Stage.1</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n">
+          <t xml:space="preserve">Stage.1</t>
+        </is>
+      </c>
+      <c r="D4" s="20">
         <v>30</v>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F4" s="20">
         <v>0</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="20">
         <v>1</v>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I4" s="20" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I4" s="20">
         <v>3</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" s="20">
         <v>1.2</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="K4" s="20">
         <v>0</v>
       </c>
-      <c r="L4" s="20" t="n">
-        <v>29</v>
+      <c r="L4" s="20">
+        <v>26</v>
       </c>
       <c r="M4" s="20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="O4" s="20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P4" s="20" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q4" s="20" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q4" s="20">
         <v>2</v>
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t>首战无回响；玩家预测锚</t>
+          <t xml:space="preserve">首战无回响；玩家预测锚</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>Encounter.2</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
+          <t xml:space="preserve">Encounter.2</t>
+        </is>
+      </c>
+      <c r="B5" s="23">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Stage.1</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="n">
+          <t xml:space="preserve">Stage.1</t>
+        </is>
+      </c>
+      <c r="D5" s="23">
         <v>30</v>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F5" s="23">
         <v>1</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="23">
         <v>0</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I5" s="23">
         <v>3</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="23">
         <v>1.2</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="23">
         <v>1</v>
       </c>
-      <c r="L5" s="23" t="n">
-        <v>32</v>
+      <c r="L5" s="23">
+        <v>28</v>
       </c>
       <c r="M5" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>LatestEncounterE1</t>
+          <t xml:space="preserve">LatestEncounterE1</t>
         </is>
       </c>
       <c r="O5" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P5" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q5" s="23">
         <v>3</v>
       </c>
       <c r="R5" s="24" t="inlineStr">
         <is>
-          <t>首次明确体验回响协同</t>
+          <t xml:space="preserve">首次明确体验回响协同</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Encounter.3</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
+          <t xml:space="preserve">Encounter.3</t>
+        </is>
+      </c>
+      <c r="B6" s="23">
         <v>3</v>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Stage.2</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="n">
+          <t xml:space="preserve">Stage.2</t>
+        </is>
+      </c>
+      <c r="D6" s="23">
         <v>30</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F6" s="23">
         <v>0.9</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="23">
         <v>0.1</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I6" s="23">
         <v>3</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="23">
         <v>1.2</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="23">
         <v>1</v>
       </c>
-      <c r="L6" s="23" t="n">
-        <v>74</v>
+      <c r="L6" s="23">
+        <v>48</v>
       </c>
       <c r="M6" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t>SelectedOrLatest</t>
+          <t xml:space="preserve">SelectedOrLatest</t>
         </is>
       </c>
       <c r="O6" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q6" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q6" s="23">
         <v>4</v>
       </c>
       <c r="R6" s="24" t="inlineStr">
         <is>
-          <t>构筑验证</t>
+          <t xml:space="preserve">构筑验证</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Encounter.4</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
+          <t xml:space="preserve">Encounter.4</t>
+        </is>
+      </c>
+      <c r="B7" s="23">
         <v>4</v>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Stage.2</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="n">
+          <t xml:space="preserve">Stage.2</t>
+        </is>
+      </c>
+      <c r="D7" s="23">
         <v>30</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F7" s="23">
         <v>0.85</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="23">
         <v>0.15</v>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I7" s="23">
         <v>4</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="23">
         <v>1.2</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="23">
         <v>1</v>
       </c>
-      <c r="L7" s="23" t="n">
-        <v>84</v>
+      <c r="L7" s="23">
+        <v>56</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>SelectedOrLatest</t>
+          <t xml:space="preserve">SelectedOrLatest</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q7" s="23">
         <v>5</v>
       </c>
       <c r="R7" s="24" t="inlineStr">
         <is>
-          <t>构筑验证</t>
+          <t xml:space="preserve">构筑验证</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Encounter.5</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
+          <t xml:space="preserve">Encounter.5</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
         <v>5</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Stage.2</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="n">
+          <t xml:space="preserve">Stage.2</t>
+        </is>
+      </c>
+      <c r="D8" s="23">
         <v>30</v>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F8" s="23">
         <v>0.8</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="23">
         <v>0.2</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I8" s="23">
         <v>4</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="23">
         <v>1.2</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="23">
         <v>1</v>
       </c>
-      <c r="L8" s="23" t="n">
-        <v>92</v>
+      <c r="L8" s="23">
+        <v>62</v>
       </c>
       <c r="M8" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t>SelectedOrLatest</t>
+          <t xml:space="preserve">SelectedOrLatest</t>
         </is>
       </c>
       <c r="O8" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q8" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q8" s="23">
         <v>6</v>
       </c>
       <c r="R8" s="24" t="inlineStr">
         <is>
-          <t>构筑验证</t>
+          <t xml:space="preserve">构筑验证</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Encounter.6</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="n">
+          <t xml:space="preserve">Encounter.6</t>
+        </is>
+      </c>
+      <c r="B9" s="23">
         <v>6</v>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Stage.3</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="n">
+          <t xml:space="preserve">Stage.3</t>
+        </is>
+      </c>
+      <c r="D9" s="23">
         <v>30</v>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F9" s="23">
         <v>0.7</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="23">
         <v>0.3</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I9" s="23">
         <v>4</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="23">
         <v>1.2</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="23">
         <v>1</v>
       </c>
-      <c r="L9" s="23" t="n">
-        <v>100</v>
+      <c r="L9" s="23">
+        <v>64</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>SelectedOrLatest</t>
+          <t xml:space="preserve">SelectedOrLatest</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q9" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q9" s="23">
         <v>7</v>
       </c>
       <c r="R9" s="24" t="inlineStr">
         <is>
-          <t>构筑验证</t>
+          <t xml:space="preserve">构筑验证</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Encounter.7</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n">
+          <t xml:space="preserve">Encounter.7</t>
+        </is>
+      </c>
+      <c r="B10" s="23">
         <v>7</v>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Stage.3</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="n">
+          <t xml:space="preserve">Stage.3</t>
+        </is>
+      </c>
+      <c r="D10" s="23">
         <v>30</v>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="n">
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="F10" s="23">
         <v>0.6</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="23">
         <v>0.4</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I10" s="23">
         <v>4</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="23">
         <v>1.2</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="23">
         <v>1</v>
       </c>
-      <c r="L10" s="23" t="n">
-        <v>104</v>
+      <c r="L10" s="23">
+        <v>76</v>
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t>SelectedOrLatest</t>
+          <t xml:space="preserve">SelectedOrLatest</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q10" s="23" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q10" s="23">
         <v>8</v>
       </c>
       <c r="R10" s="24" t="inlineStr">
         <is>
-          <t>Boss前最终普通战</t>
+          <t xml:space="preserve">Boss前最终普通战</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>Encounter.8</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="n">
+          <t xml:space="preserve">Encounter.8</t>
+        </is>
+      </c>
+      <c r="B11" s="26">
         <v>8</v>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>Stage.Boss</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="n">
+          <t xml:space="preserve">Stage.Boss</t>
+        </is>
+      </c>
+      <c r="D11" s="26">
         <v>0</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>BossOrPlayerDeath</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="n">
+          <t xml:space="preserve">BossOrPlayerDeath</t>
+        </is>
+      </c>
+      <c r="F11" s="26">
         <v>0.5</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="26">
         <v>0.5</v>
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>AllLocked</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="n">
+          <t xml:space="preserve">AllLocked</t>
+        </is>
+      </c>
+      <c r="I11" s="26">
         <v>4</v>
       </c>
-      <c r="J11" s="26" t="n">
+      <c r="J11" s="26">
         <v>1.2</v>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="K11" s="26">
         <v>1</v>
       </c>
-      <c r="L11" s="26" t="n">
-        <v>100</v>
+      <c r="L11" s="26">
+        <v>50</v>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>false</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="N11" s="26" t="inlineStr">
         <is>
-          <t>LatestEncounterE1</t>
+          <t xml:space="preserve">LatestEncounterE1</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="P11" s="26" t="inlineStr">
         <is>
-          <t>关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q11" s="26" t="n">
+          <t xml:space="preserve">关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q11" s="26">
         <v>9</v>
       </c>
       <c r="R11" s="27" t="inlineStr">
         <is>
-          <t>Boss不计入24个增援上限</t>
+          <t xml:space="preserve">Boss不计入50个增援上限</t>
         </is>
       </c>
     </row>
@@ -1763,1108 +1763,1108 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>Encounter.1.Wave.1</t>
+          <t xml:space="preserve">Encounter.1.Wave.1</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Encounter.1</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="n">
+          <t xml:space="preserve">Encounter.1</t>
+        </is>
+      </c>
+      <c r="C4" s="20">
         <v>1</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="20">
         <v>0</v>
       </c>
-      <c r="E4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="20" t="n">
+      <c r="E4" s="20">
+        <v>12</v>
+      </c>
+      <c r="F4" s="20">
+        <v>2</v>
+      </c>
+      <c r="G4" s="20">
         <v>0</v>
       </c>
-      <c r="H4" s="20" t="n"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K4" s="20" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K4" s="20">
         <v>1</v>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>Encounter.1.Wave.2</t>
+          <t xml:space="preserve">Encounter.1.Wave.2</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Encounter.1</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="n">
+          <t xml:space="preserve">Encounter.1</t>
+        </is>
+      </c>
+      <c r="C5" s="23">
         <v>2</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="23">
         <v>10</v>
       </c>
-      <c r="E5" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="23" t="n">
+      <c r="E5" s="23">
+        <v>12</v>
+      </c>
+      <c r="F5" s="23">
+        <v>2</v>
+      </c>
+      <c r="G5" s="23">
         <v>0</v>
       </c>
-      <c r="H5" s="23" t="n"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K5" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>1</v>
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Encounter.1.Wave.3</t>
+          <t xml:space="preserve">Encounter.1.Wave.3</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Encounter.1</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="n">
+          <t xml:space="preserve">Encounter.1</t>
+        </is>
+      </c>
+      <c r="C6" s="23">
         <v>3</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="23">
         <v>20</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="23" t="n">
+      <c r="E6" s="23">
+        <v>13</v>
+      </c>
+      <c r="F6" s="23">
+        <v>2</v>
+      </c>
+      <c r="G6" s="23">
         <v>0</v>
       </c>
-      <c r="H6" s="23" t="n"/>
+      <c r="H6" s="23"/>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>1</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Encounter.2.Wave.1</t>
+          <t xml:space="preserve">Encounter.2.Wave.1</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Encounter.2</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="n">
+          <t xml:space="preserve">Encounter.2</t>
+        </is>
+      </c>
+      <c r="C7" s="23">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="23">
         <v>0</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="23" t="n">
+      <c r="E7" s="23">
+        <v>13</v>
+      </c>
+      <c r="F7" s="23">
+        <v>2</v>
+      </c>
+      <c r="G7" s="23">
         <v>0</v>
       </c>
-      <c r="H7" s="23" t="n"/>
+      <c r="H7" s="23"/>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>2</v>
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Encounter.2.Wave.2</t>
+          <t xml:space="preserve">Encounter.2.Wave.2</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Encounter.2</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="n">
+          <t xml:space="preserve">Encounter.2</t>
+        </is>
+      </c>
+      <c r="C8" s="23">
         <v>2</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="23">
         <v>10</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="23" t="n">
+      <c r="E8" s="23">
+        <v>14</v>
+      </c>
+      <c r="F8" s="23">
+        <v>3</v>
+      </c>
+      <c r="G8" s="23">
         <v>0</v>
       </c>
-      <c r="H8" s="23" t="n"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K8" s="23">
         <v>2</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Encounter.2.Wave.3</t>
+          <t xml:space="preserve">Encounter.2.Wave.3</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Encounter.2</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="n">
+          <t xml:space="preserve">Encounter.2</t>
+        </is>
+      </c>
+      <c r="C9" s="23">
         <v>3</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="23">
         <v>20</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="23" t="n">
+      <c r="E9" s="23">
+        <v>11</v>
+      </c>
+      <c r="F9" s="23">
+        <v>3</v>
+      </c>
+      <c r="G9" s="23">
         <v>0</v>
       </c>
-      <c r="H9" s="23" t="n"/>
+      <c r="H9" s="23"/>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K9" s="23">
         <v>2</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>第一关整关不刷精英</t>
+          <t xml:space="preserve">第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Encounter.3.Wave.1</t>
+          <t xml:space="preserve">Encounter.3.Wave.1</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Encounter.3</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="n">
+          <t xml:space="preserve">Encounter.3</t>
+        </is>
+      </c>
+      <c r="C10" s="23">
         <v>1</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="23">
         <v>0</v>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="23" t="n"/>
+      <c r="E10" s="23">
+        <v>21</v>
+      </c>
+      <c r="F10" s="23">
+        <v>3</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2</v>
+      </c>
+      <c r="H10" s="23"/>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K10" s="23">
         <v>3</v>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Encounter.3.Wave.2</t>
+          <t xml:space="preserve">Encounter.3.Wave.2</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Encounter.3</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="n">
+          <t xml:space="preserve">Encounter.3</t>
+        </is>
+      </c>
+      <c r="C11" s="23">
         <v>2</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="23">
         <v>10</v>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="23" t="n"/>
+      <c r="E11" s="23">
+        <v>22</v>
+      </c>
+      <c r="F11" s="23">
+        <v>3</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1</v>
+      </c>
+      <c r="H11" s="23"/>
       <c r="I11" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K11" s="23">
         <v>3</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Encounter.3.Wave.3</t>
+          <t xml:space="preserve">Encounter.3.Wave.3</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Encounter.3</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="n">
+          <t xml:space="preserve">Encounter.3</t>
+        </is>
+      </c>
+      <c r="C12" s="23">
         <v>3</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="23">
         <v>20</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="23">
         <v>24</v>
       </c>
-      <c r="F12" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" s="23" t="n"/>
+      <c r="F12" s="23">
+        <v>3</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1</v>
+      </c>
+      <c r="H12" s="23"/>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K12" s="23">
         <v>3</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>Encounter.4.Wave.1</t>
+          <t xml:space="preserve">Encounter.4.Wave.1</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Encounter.4</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="n">
+          <t xml:space="preserve">Encounter.4</t>
+        </is>
+      </c>
+      <c r="C13" s="23">
         <v>1</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="23">
         <v>0</v>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="23" t="n">
+      <c r="E13" s="23">
+        <v>26</v>
+      </c>
+      <c r="F13" s="23">
         <v>6</v>
       </c>
-      <c r="H13" s="23" t="n"/>
+      <c r="G13" s="23">
+        <v>4</v>
+      </c>
+      <c r="H13" s="23"/>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K13" s="23">
         <v>4</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>Encounter.4.Wave.2</t>
+          <t xml:space="preserve">Encounter.4.Wave.2</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Encounter.4</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="n">
+          <t xml:space="preserve">Encounter.4</t>
+        </is>
+      </c>
+      <c r="C14" s="23">
         <v>2</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="23">
         <v>10</v>
       </c>
-      <c r="E14" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="23" t="n">
+      <c r="E14" s="23">
+        <v>22</v>
+      </c>
+      <c r="F14" s="23">
         <v>7</v>
       </c>
-      <c r="H14" s="23" t="n"/>
+      <c r="G14" s="23">
+        <v>3</v>
+      </c>
+      <c r="H14" s="23"/>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K14" s="23">
         <v>4</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>Encounter.4.Wave.3</t>
+          <t xml:space="preserve">Encounter.4.Wave.3</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Encounter.4</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="n">
+          <t xml:space="preserve">Encounter.4</t>
+        </is>
+      </c>
+      <c r="C15" s="23">
         <v>3</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="23">
         <v>20</v>
       </c>
-      <c r="E15" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="23" t="n"/>
+      <c r="E15" s="23">
+        <v>28</v>
+      </c>
+      <c r="F15" s="23">
+        <v>9</v>
+      </c>
+      <c r="G15" s="23">
+        <v>2</v>
+      </c>
+      <c r="H15" s="23"/>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K15" s="23">
         <v>4</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>Encounter.5.Wave.1</t>
+          <t xml:space="preserve">Encounter.5.Wave.1</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Encounter.5</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="n">
+          <t xml:space="preserve">Encounter.5</t>
+        </is>
+      </c>
+      <c r="C16" s="23">
         <v>1</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="23">
         <v>0</v>
       </c>
-      <c r="E16" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="F16" s="23" t="n">
+      <c r="E16" s="23">
+        <v>33</v>
+      </c>
+      <c r="F16" s="23">
         <v>11</v>
       </c>
-      <c r="G16" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="23" t="n"/>
+      <c r="G16" s="23">
+        <v>4</v>
+      </c>
+      <c r="H16" s="23"/>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K16" s="23">
         <v>5</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>Encounter.5.Wave.2</t>
+          <t xml:space="preserve">Encounter.5.Wave.2</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Encounter.5</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="n">
+          <t xml:space="preserve">Encounter.5</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
         <v>2</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="23">
         <v>10</v>
       </c>
-      <c r="E17" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="23" t="n"/>
+      <c r="E17" s="23">
+        <v>30</v>
+      </c>
+      <c r="F17" s="23">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23">
+        <v>3</v>
+      </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K17" s="23">
         <v>5</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Encounter.5.Wave.3</t>
+          <t xml:space="preserve">Encounter.5.Wave.3</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Encounter.5</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="n">
+          <t xml:space="preserve">Encounter.5</t>
+        </is>
+      </c>
+      <c r="C18" s="23">
         <v>3</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="23">
         <v>20</v>
       </c>
-      <c r="E18" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="23" t="n"/>
+      <c r="E18" s="23">
+        <v>38</v>
+      </c>
+      <c r="F18" s="23">
+        <v>14</v>
+      </c>
+      <c r="G18" s="23">
+        <v>3</v>
+      </c>
+      <c r="H18" s="23"/>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K18" s="23">
         <v>5</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>Encounter.6.Wave.1</t>
+          <t xml:space="preserve">Encounter.6.Wave.1</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Encounter.6</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="n">
+          <t xml:space="preserve">Encounter.6</t>
+        </is>
+      </c>
+      <c r="C19" s="23">
         <v>1</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="23">
         <v>0</v>
       </c>
-      <c r="E19" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="23" t="n"/>
+      <c r="E19" s="23">
+        <v>33</v>
+      </c>
+      <c r="F19" s="23">
+        <v>12</v>
+      </c>
+      <c r="G19" s="23">
+        <v>5</v>
+      </c>
+      <c r="H19" s="23"/>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K19" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K19" s="23">
         <v>6</v>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Encounter.6.Wave.2</t>
+          <t xml:space="preserve">Encounter.6.Wave.2</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Encounter.6</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="n">
+          <t xml:space="preserve">Encounter.6</t>
+        </is>
+      </c>
+      <c r="C20" s="23">
         <v>2</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="23">
         <v>10</v>
       </c>
-      <c r="E20" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="23" t="n"/>
+      <c r="E20" s="23">
+        <v>32</v>
+      </c>
+      <c r="F20" s="23">
+        <v>14</v>
+      </c>
+      <c r="G20" s="23">
+        <v>5</v>
+      </c>
+      <c r="H20" s="23"/>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K20" s="23">
         <v>6</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>Encounter.6.Wave.3</t>
+          <t xml:space="preserve">Encounter.6.Wave.3</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Encounter.6</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="n">
+          <t xml:space="preserve">Encounter.6</t>
+        </is>
+      </c>
+      <c r="C21" s="23">
         <v>3</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="23">
         <v>20</v>
       </c>
-      <c r="E21" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="23" t="n"/>
+      <c r="E21" s="23">
+        <v>40</v>
+      </c>
+      <c r="F21" s="23">
+        <v>14</v>
+      </c>
+      <c r="G21" s="23">
+        <v>6</v>
+      </c>
+      <c r="H21" s="23"/>
       <c r="I21" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K21" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K21" s="23">
         <v>6</v>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>Encounter.7.Wave.1</t>
+          <t xml:space="preserve">Encounter.7.Wave.1</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Encounter.7</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n">
+          <t xml:space="preserve">Encounter.7</t>
+        </is>
+      </c>
+      <c r="C22" s="23">
         <v>1</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="23">
         <v>0</v>
       </c>
-      <c r="E22" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" s="23" t="n"/>
+      <c r="E22" s="23">
+        <v>42</v>
+      </c>
+      <c r="F22" s="23">
+        <v>16</v>
+      </c>
+      <c r="G22" s="23">
+        <v>8</v>
+      </c>
+      <c r="H22" s="23"/>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K22" s="23">
         <v>7</v>
       </c>
       <c r="L22" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>Encounter.7.Wave.2</t>
+          <t xml:space="preserve">Encounter.7.Wave.2</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Encounter.7</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="n">
+          <t xml:space="preserve">Encounter.7</t>
+        </is>
+      </c>
+      <c r="C23" s="23">
         <v>2</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="23">
         <v>10</v>
       </c>
-      <c r="E23" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="F23" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G23" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H23" s="23" t="n"/>
+      <c r="E23" s="23">
+        <v>40</v>
+      </c>
+      <c r="F23" s="23">
+        <v>16</v>
+      </c>
+      <c r="G23" s="23">
+        <v>6</v>
+      </c>
+      <c r="H23" s="23"/>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K23" s="23">
         <v>7</v>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>Encounter.7.Wave.3</t>
+          <t xml:space="preserve">Encounter.7.Wave.3</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Encounter.7</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="n">
+          <t xml:space="preserve">Encounter.7</t>
+        </is>
+      </c>
+      <c r="C24" s="23">
         <v>3</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="23">
         <v>20</v>
       </c>
-      <c r="E24" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="23" t="n"/>
+      <c r="E24" s="23">
+        <v>47</v>
+      </c>
+      <c r="F24" s="23">
+        <v>18</v>
+      </c>
+      <c r="G24" s="23">
+        <v>8</v>
+      </c>
+      <c r="H24" s="23"/>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K24" s="23">
         <v>7</v>
       </c>
       <c r="L24" s="24" t="inlineStr">
         <is>
-          <t>企微《怪物》投放成长表</t>
+          <t xml:space="preserve">企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Encounter.8.Wave.1</t>
+          <t xml:space="preserve">Encounter.8.Wave.1</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Encounter.8</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="n">
+          <t xml:space="preserve">Encounter.8</t>
+        </is>
+      </c>
+      <c r="C25" s="26">
         <v>1</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="26">
         <v>0</v>
       </c>
-      <c r="E25" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="F25" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" s="26" t="n">
-        <v>7</v>
+      <c r="E25" s="26">
+        <v>40</v>
+      </c>
+      <c r="F25" s="26">
+        <v>10</v>
+      </c>
+      <c r="G25" s="26">
+        <v>4</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>M_SHEEP</t>
+          <t xml:space="preserve">M_SHEEP</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K25" s="26">
         <v>8</v>
       </c>
       <c r="L25" s="27" t="inlineStr">
         <is>
-          <t>Boss在0秒刷新；16近战/8远程/5精英援军</t>
+          <t xml:space="preserve">Boss在0秒刷新；40近战/10远程/4精英援军</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>Encounter.8.Wave.2</t>
+          <t xml:space="preserve">Encounter.8.Wave.2</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>Encounter.8</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="n">
+          <t xml:space="preserve">Encounter.8</t>
+        </is>
+      </c>
+      <c r="C26" s="26">
         <v>2</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="26">
         <v>10</v>
       </c>
-      <c r="E26" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="G26" s="26" t="n">
+      <c r="E26" s="26">
+        <v>30</v>
+      </c>
+      <c r="F26" s="26">
         <v>10</v>
       </c>
-      <c r="H26" s="26" t="n"/>
+      <c r="G26" s="26">
+        <v>5</v>
+      </c>
+      <c r="H26" s="26"/>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J26" s="26" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K26" s="26" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K26" s="26">
         <v>8</v>
       </c>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t>Boss关增援波</t>
+          <t xml:space="preserve">Boss关增援波</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>Encounter.8.Wave.3</t>
+          <t xml:space="preserve">Encounter.8.Wave.3</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>Encounter.8</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="n">
+          <t xml:space="preserve">Encounter.8</t>
+        </is>
+      </c>
+      <c r="C27" s="26">
         <v>3</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="26">
         <v>20</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="26">
         <v>36</v>
       </c>
-      <c r="F27" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="H27" s="26" t="n"/>
+      <c r="F27" s="26">
+        <v>12</v>
+      </c>
+      <c r="G27" s="26">
+        <v>7</v>
+      </c>
+      <c r="H27" s="26"/>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J27" s="26" t="inlineStr">
         <is>
-          <t>企微怪物表</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="n">
+          <t xml:space="preserve">企微怪物表</t>
+        </is>
+      </c>
+      <c r="K27" s="26">
         <v>8</v>
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t>Boss关增援波</t>
+          <t xml:space="preserve">Boss关增援波</t>
         </is>
       </c>
     </row>
@@ -2989,171 +2989,171 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>Spawn.Melee</t>
+          <t xml:space="preserve">Spawn.Melee</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Melee</t>
+          <t xml:space="preserve">Melee</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>M_SLIME</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n">
+          <t xml:space="preserve">M_SLIME</t>
+        </is>
+      </c>
+      <c r="D4" s="20">
         <v>620</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="20">
         <v>820</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="20">
         <v>110</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="20">
         <v>0.8</v>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>NormalAroundAnchor</t>
+          <t xml:space="preserve">NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>Explicit</t>
+          <t xml:space="preserve">Explicit</t>
         </is>
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="K4" s="20" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
-        </is>
-      </c>
-      <c r="L4" s="20" t="n">
+          <t xml:space="preserve">刷怪规则</t>
+        </is>
+      </c>
+      <c r="L4" s="20">
         <v>9</v>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>近战出生参数</t>
+          <t xml:space="preserve">近战出生参数</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>Spawn.Ranged</t>
+          <t xml:space="preserve">Spawn.Ranged</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Ranged</t>
+          <t xml:space="preserve">Ranged</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>M_RABBIT</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="n">
+          <t xml:space="preserve">M_RABBIT</t>
+        </is>
+      </c>
+      <c r="D5" s="23">
         <v>750</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="23">
         <v>1000</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="23">
         <v>125</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="23">
         <v>0.8</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>NormalAroundAnchor</t>
+          <t xml:space="preserve">NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>Explicit</t>
+          <t xml:space="preserve">Explicit</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
-        </is>
-      </c>
-      <c r="L5" s="23" t="n">
+          <t xml:space="preserve">刷怪规则</t>
+        </is>
+      </c>
+      <c r="L5" s="23">
         <v>10</v>
       </c>
       <c r="M5" s="24" t="inlineStr">
         <is>
-          <t>远程出生参数</t>
+          <t xml:space="preserve">远程出生参数</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Spawn.Elite</t>
+          <t xml:space="preserve">Spawn.Elite</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t xml:space="preserve">Elite</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>M_FOX</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="n">
+          <t xml:space="preserve">M_FOX</t>
+        </is>
+      </c>
+      <c r="D6" s="23">
         <v>700</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="23">
         <v>900</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="23">
         <v>200</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="23">
         <v>1</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>NormalAroundAnchor</t>
+          <t xml:space="preserve">NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>Explicit</t>
+          <t xml:space="preserve">Explicit</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>刷怪规则</t>
-        </is>
-      </c>
-      <c r="L6" s="23" t="n">
+          <t xml:space="preserve">刷怪规则</t>
+        </is>
+      </c>
+      <c r="L6" s="23">
         <v>11</v>
       </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t>精英出生参数</t>
+          <t xml:space="preserve">精英出生参数</t>
         </is>
       </c>
     </row>

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Encounters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EncounterWaves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SpawnProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SpawnPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_ExportMap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -609,12 +609,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.5" customWidth="1" min="1" max="1"/>
@@ -637,6 +637,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -700,42 +701,44 @@
           <t>Stage.1</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
-        <v>1</v>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
           <t>SC01</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="20" t="b">
+        <v>1</v>
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>关卡配置表</t>
         </is>
       </c>
-      <c r="J4" s="20" t="n">
-        <v>2</v>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
@@ -749,42 +752,44 @@
           <t>Stage.2</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
-        <v>2</v>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
           <t>SC02</t>
         </is>
       </c>
-      <c r="D5" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
           <t>关卡配置表</t>
         </is>
       </c>
-      <c r="J5" s="23" t="n">
-        <v>4</v>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K5" s="24" t="inlineStr">
         <is>
@@ -798,42 +803,44 @@
           <t>Stage.3</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
-        <v>3</v>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
           <t>SC03</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
           <t>关卡配置表</t>
         </is>
       </c>
-      <c r="J6" s="23" t="n">
-        <v>7</v>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
@@ -847,42 +854,44 @@
           <t>Stage.Boss</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
-        <v>4</v>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
           <t>SC04</t>
         </is>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
           <t>关卡配置表</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n">
-        <v>9</v>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K7" s="27" t="inlineStr">
         <is>
@@ -890,11 +899,17 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <dataValidations count="4">
     <dataValidation sqref="C4:C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"Level00"</formula1>
@@ -909,20 +924,16 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.13000106811523" customWidth="1" min="1" max="1"/>
@@ -952,6 +963,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1047,600 +1059,718 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1</t>
-        </is>
-      </c>
-      <c r="B4" s="20">
-        <v>1</v>
+          <t>Encounter.1</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.1</t>
-        </is>
-      </c>
-      <c r="D4" s="20">
-        <v>30</v>
+          <t>Stage.1</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F4" s="20">
-        <v>0</v>
-      </c>
-      <c r="G4" s="20">
-        <v>1</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I4" s="20">
-        <v>3</v>
-      </c>
-      <c r="J4" s="20">
-        <v>1.2</v>
-      </c>
-      <c r="K4" s="20">
-        <v>0</v>
-      </c>
-      <c r="L4" s="20">
-        <v>26</v>
-      </c>
-      <c r="M4" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="b">
+        <v>1</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="O4" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O4" s="20" t="b">
+        <v>1</v>
       </c>
       <c r="P4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q4" s="20">
-        <v>2</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q4" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">首战无回响；玩家预测锚</t>
+          <t>首战无回响；玩家预测锚</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2</t>
-        </is>
-      </c>
-      <c r="B5" s="23">
-        <v>2</v>
+          <t>Encounter.2</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.1</t>
-        </is>
-      </c>
-      <c r="D5" s="23">
-        <v>30</v>
+          <t>Stage.1</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F5" s="23">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I5" s="23">
-        <v>3</v>
-      </c>
-      <c r="J5" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K5" s="23">
-        <v>1</v>
-      </c>
-      <c r="L5" s="23">
-        <v>28</v>
-      </c>
-      <c r="M5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M5" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LatestEncounterE1</t>
-        </is>
-      </c>
-      <c r="O5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>LatestEncounterE1</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q5" s="23">
-        <v>3</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="R5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">首次明确体验回响协同</t>
+          <t>首次明确体验回响协同</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <v>3</v>
+          <t>Encounter.3</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.2</t>
-        </is>
-      </c>
-      <c r="D6" s="23">
-        <v>30</v>
+          <t>Stage.2</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F6" s="23">
-        <v>0.9</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.1</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I6" s="23">
-        <v>3</v>
-      </c>
-      <c r="J6" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K6" s="23">
-        <v>1</v>
-      </c>
-      <c r="L6" s="23">
-        <v>48</v>
-      </c>
-      <c r="M6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SelectedOrLatest</t>
-        </is>
-      </c>
-      <c r="O6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>SelectedOrLatest</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q6" s="23">
-        <v>4</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q6" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="R6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">构筑验证</t>
+          <t>构筑验证</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4</t>
-        </is>
-      </c>
-      <c r="B7" s="23">
-        <v>4</v>
+          <t>Encounter.4</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.2</t>
-        </is>
-      </c>
-      <c r="D7" s="23">
-        <v>30</v>
+          <t>Stage.2</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F7" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0.15</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I7" s="23">
-        <v>4</v>
-      </c>
-      <c r="J7" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K7" s="23">
-        <v>1</v>
-      </c>
-      <c r="L7" s="23">
-        <v>56</v>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SelectedOrLatest</t>
-        </is>
-      </c>
-      <c r="O7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>SelectedOrLatest</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q7" s="23">
-        <v>5</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="R7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">构筑验证</t>
+          <t>构筑验证</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5</t>
-        </is>
-      </c>
-      <c r="B8" s="23">
-        <v>5</v>
+          <t>Encounter.5</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.2</t>
-        </is>
-      </c>
-      <c r="D8" s="23">
-        <v>30</v>
+          <t>Stage.2</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F8" s="23">
-        <v>0.8</v>
-      </c>
-      <c r="G8" s="23">
-        <v>0.2</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I8" s="23">
-        <v>4</v>
-      </c>
-      <c r="J8" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K8" s="23">
-        <v>1</v>
-      </c>
-      <c r="L8" s="23">
-        <v>62</v>
-      </c>
-      <c r="M8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SelectedOrLatest</t>
-        </is>
-      </c>
-      <c r="O8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>SelectedOrLatest</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q8" s="23">
-        <v>6</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="R8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">构筑验证</t>
+          <t>构筑验证</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <v>6</v>
+          <t>Encounter.6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.3</t>
-        </is>
-      </c>
-      <c r="D9" s="23">
-        <v>30</v>
+          <t>Stage.3</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F9" s="23">
-        <v>0.7</v>
-      </c>
-      <c r="G9" s="23">
-        <v>0.3</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I9" s="23">
-        <v>4</v>
-      </c>
-      <c r="J9" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K9" s="23">
-        <v>1</v>
-      </c>
-      <c r="L9" s="23">
-        <v>64</v>
-      </c>
-      <c r="M9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SelectedOrLatest</t>
-        </is>
-      </c>
-      <c r="O9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>SelectedOrLatest</t>
+        </is>
+      </c>
+      <c r="O9" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q9" s="23">
-        <v>7</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="R9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">构筑验证</t>
+          <t>构筑验证</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7</t>
-        </is>
-      </c>
-      <c r="B10" s="23">
-        <v>7</v>
+          <t>Encounter.7</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.3</t>
-        </is>
-      </c>
-      <c r="D10" s="23">
-        <v>30</v>
+          <t>Stage.3</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
-        </is>
-      </c>
-      <c r="F10" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.4</v>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I10" s="23">
-        <v>4</v>
-      </c>
-      <c r="J10" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="K10" s="23">
-        <v>1</v>
-      </c>
-      <c r="L10" s="23">
-        <v>76</v>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="N10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SelectedOrLatest</t>
-        </is>
-      </c>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>SelectedOrLatest</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="P10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q10" s="23">
-        <v>8</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="R10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss前最终普通战</t>
+          <t>Boss前最终普通战</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8</t>
-        </is>
-      </c>
-      <c r="B11" s="26">
-        <v>8</v>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage.Boss</t>
-        </is>
-      </c>
-      <c r="D11" s="26">
+          <t>Stage.Boss</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>BossOrPlayerDeath</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>AllLocked</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BossOrPlayerDeath</t>
-        </is>
-      </c>
-      <c r="F11" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AllLocked</t>
-        </is>
-      </c>
-      <c r="I11" s="26">
-        <v>4</v>
-      </c>
-      <c r="J11" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="K11" s="26">
-        <v>1</v>
-      </c>
-      <c r="L11" s="26">
-        <v>50</v>
-      </c>
-      <c r="M11" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
       <c r="N11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LatestEncounterE1</t>
-        </is>
-      </c>
-      <c r="O11" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>LatestEncounterE1</t>
+        </is>
+      </c>
+      <c r="O11" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="P11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">关卡配置表</t>
-        </is>
-      </c>
-      <c r="Q11" s="26">
-        <v>9</v>
+          <t>关卡配置表</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="R11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss不计入50个增援上限</t>
-        </is>
-      </c>
-    </row>
+          <t>Boss不计入50个增援上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <dataValidations count="6">
     <dataValidation sqref="C4:C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblStages[Id]")</formula1>
@@ -1661,20 +1791,16 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.38000106811523" customWidth="1" min="1" max="1"/>
@@ -1698,6 +1824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1763,1116 +1890,1362 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1.Wave.1</t>
+          <t>Encounter.1.Wave.1</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1</t>
-        </is>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>0</v>
-      </c>
-      <c r="E4" s="20">
-        <v>12</v>
-      </c>
-      <c r="F4" s="20">
-        <v>2</v>
-      </c>
-      <c r="G4" s="20">
-        <v>0</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.1</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr"/>
+      <c r="I4" s="20" t="b">
+        <v>1</v>
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K4" s="20">
-        <v>1</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1.Wave.2</t>
+          <t>Encounter.1.Wave.2</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1</t>
-        </is>
-      </c>
-      <c r="C5" s="23">
-        <v>2</v>
-      </c>
-      <c r="D5" s="23">
-        <v>10</v>
-      </c>
-      <c r="E5" s="23">
-        <v>12</v>
-      </c>
-      <c r="F5" s="23">
-        <v>2</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.1</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr"/>
+      <c r="I5" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K5" s="23">
-        <v>1</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1.Wave.3</t>
+          <t>Encounter.1.Wave.3</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.1</t>
-        </is>
-      </c>
-      <c r="C6" s="23">
-        <v>3</v>
-      </c>
-      <c r="D6" s="23">
-        <v>20</v>
-      </c>
-      <c r="E6" s="23">
-        <v>13</v>
-      </c>
-      <c r="F6" s="23">
-        <v>2</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0</v>
-      </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.1</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr"/>
+      <c r="I6" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K6" s="23">
-        <v>1</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2.Wave.1</t>
+          <t>Encounter.2.Wave.1</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2</t>
-        </is>
-      </c>
-      <c r="C7" s="23">
-        <v>1</v>
-      </c>
-      <c r="D7" s="23">
-        <v>0</v>
-      </c>
-      <c r="E7" s="23">
-        <v>13</v>
-      </c>
-      <c r="F7" s="23">
-        <v>2</v>
-      </c>
-      <c r="G7" s="23">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.2</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr"/>
+      <c r="I7" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K7" s="23">
-        <v>2</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2.Wave.2</t>
+          <t>Encounter.2.Wave.2</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2</t>
-        </is>
-      </c>
-      <c r="C8" s="23">
-        <v>2</v>
-      </c>
-      <c r="D8" s="23">
-        <v>10</v>
-      </c>
-      <c r="E8" s="23">
-        <v>14</v>
-      </c>
-      <c r="F8" s="23">
-        <v>3</v>
-      </c>
-      <c r="G8" s="23">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.2</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr"/>
+      <c r="I8" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K8" s="23">
-        <v>2</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2.Wave.3</t>
+          <t>Encounter.2.Wave.3</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.2</t>
-        </is>
-      </c>
-      <c r="C9" s="23">
-        <v>3</v>
-      </c>
-      <c r="D9" s="23">
-        <v>20</v>
-      </c>
-      <c r="E9" s="23">
-        <v>11</v>
-      </c>
-      <c r="F9" s="23">
-        <v>3</v>
-      </c>
-      <c r="G9" s="23">
-        <v>0</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.2</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr"/>
+      <c r="I9" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K9" s="23">
-        <v>2</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">第一关整关不刷精英</t>
+          <t>第一关整关不刷精英</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3.Wave.1</t>
+          <t>Encounter.3.Wave.1</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3</t>
-        </is>
-      </c>
-      <c r="C10" s="23">
-        <v>1</v>
-      </c>
-      <c r="D10" s="23">
-        <v>0</v>
-      </c>
-      <c r="E10" s="23">
-        <v>21</v>
-      </c>
-      <c r="F10" s="23">
-        <v>3</v>
-      </c>
-      <c r="G10" s="23">
-        <v>2</v>
-      </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.3</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr"/>
+      <c r="I10" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K10" s="23">
-        <v>3</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3.Wave.2</t>
+          <t>Encounter.3.Wave.2</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3</t>
-        </is>
-      </c>
-      <c r="C11" s="23">
-        <v>2</v>
-      </c>
-      <c r="D11" s="23">
-        <v>10</v>
-      </c>
-      <c r="E11" s="23">
-        <v>22</v>
-      </c>
-      <c r="F11" s="23">
-        <v>3</v>
-      </c>
-      <c r="G11" s="23">
-        <v>1</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.3</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr"/>
+      <c r="I11" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K11" s="23">
-        <v>3</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3.Wave.3</t>
+          <t>Encounter.3.Wave.3</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.3</t>
-        </is>
-      </c>
-      <c r="C12" s="23">
-        <v>3</v>
-      </c>
-      <c r="D12" s="23">
-        <v>20</v>
-      </c>
-      <c r="E12" s="23">
-        <v>24</v>
-      </c>
-      <c r="F12" s="23">
-        <v>3</v>
-      </c>
-      <c r="G12" s="23">
-        <v>1</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.3</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr"/>
+      <c r="I12" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K12" s="23">
-        <v>3</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4.Wave.1</t>
+          <t>Encounter.4.Wave.1</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4</t>
-        </is>
-      </c>
-      <c r="C13" s="23">
-        <v>1</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23">
-        <v>26</v>
-      </c>
-      <c r="F13" s="23">
-        <v>6</v>
-      </c>
-      <c r="G13" s="23">
-        <v>4</v>
-      </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.4</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr"/>
+      <c r="I13" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K13" s="23">
-        <v>4</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4.Wave.2</t>
+          <t>Encounter.4.Wave.2</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4</t>
-        </is>
-      </c>
-      <c r="C14" s="23">
-        <v>2</v>
-      </c>
-      <c r="D14" s="23">
-        <v>10</v>
-      </c>
-      <c r="E14" s="23">
-        <v>22</v>
-      </c>
-      <c r="F14" s="23">
-        <v>7</v>
-      </c>
-      <c r="G14" s="23">
-        <v>3</v>
-      </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.4</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr"/>
+      <c r="I14" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K14" s="23">
-        <v>4</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4.Wave.3</t>
+          <t>Encounter.4.Wave.3</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.4</t>
-        </is>
-      </c>
-      <c r="C15" s="23">
-        <v>3</v>
-      </c>
-      <c r="D15" s="23">
-        <v>20</v>
-      </c>
-      <c r="E15" s="23">
-        <v>28</v>
-      </c>
-      <c r="F15" s="23">
-        <v>9</v>
-      </c>
-      <c r="G15" s="23">
-        <v>2</v>
-      </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.4</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr"/>
+      <c r="I15" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K15" s="23">
-        <v>4</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5.Wave.1</t>
+          <t>Encounter.5.Wave.1</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5</t>
-        </is>
-      </c>
-      <c r="C16" s="23">
-        <v>1</v>
-      </c>
-      <c r="D16" s="23">
-        <v>0</v>
-      </c>
-      <c r="E16" s="23">
-        <v>33</v>
-      </c>
-      <c r="F16" s="23">
-        <v>11</v>
-      </c>
-      <c r="G16" s="23">
-        <v>4</v>
-      </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.5</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr"/>
+      <c r="I16" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K16" s="23">
-        <v>5</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5.Wave.2</t>
+          <t>Encounter.5.Wave.2</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5</t>
-        </is>
-      </c>
-      <c r="C17" s="23">
-        <v>2</v>
-      </c>
-      <c r="D17" s="23">
-        <v>10</v>
-      </c>
-      <c r="E17" s="23">
-        <v>30</v>
-      </c>
-      <c r="F17" s="23">
-        <v>12</v>
-      </c>
-      <c r="G17" s="23">
-        <v>3</v>
-      </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.5</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr"/>
+      <c r="I17" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K17" s="23">
-        <v>5</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5.Wave.3</t>
+          <t>Encounter.5.Wave.3</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.5</t>
-        </is>
-      </c>
-      <c r="C18" s="23">
-        <v>3</v>
-      </c>
-      <c r="D18" s="23">
-        <v>20</v>
-      </c>
-      <c r="E18" s="23">
-        <v>38</v>
-      </c>
-      <c r="F18" s="23">
-        <v>14</v>
-      </c>
-      <c r="G18" s="23">
-        <v>3</v>
-      </c>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.5</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr"/>
+      <c r="I18" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K18" s="23">
-        <v>5</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6.Wave.1</t>
+          <t>Encounter.6.Wave.1</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6</t>
-        </is>
-      </c>
-      <c r="C19" s="23">
-        <v>1</v>
-      </c>
-      <c r="D19" s="23">
-        <v>0</v>
-      </c>
-      <c r="E19" s="23">
-        <v>33</v>
-      </c>
-      <c r="F19" s="23">
-        <v>12</v>
-      </c>
-      <c r="G19" s="23">
-        <v>5</v>
-      </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.6</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr"/>
+      <c r="I19" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K19" s="23">
-        <v>6</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6.Wave.2</t>
+          <t>Encounter.6.Wave.2</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6</t>
-        </is>
-      </c>
-      <c r="C20" s="23">
-        <v>2</v>
-      </c>
-      <c r="D20" s="23">
-        <v>10</v>
-      </c>
-      <c r="E20" s="23">
-        <v>32</v>
-      </c>
-      <c r="F20" s="23">
-        <v>14</v>
-      </c>
-      <c r="G20" s="23">
-        <v>5</v>
-      </c>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.6</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr"/>
+      <c r="I20" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K20" s="23">
-        <v>6</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6.Wave.3</t>
+          <t>Encounter.6.Wave.3</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.6</t>
-        </is>
-      </c>
-      <c r="C21" s="23">
-        <v>3</v>
-      </c>
-      <c r="D21" s="23">
-        <v>20</v>
-      </c>
-      <c r="E21" s="23">
-        <v>40</v>
-      </c>
-      <c r="F21" s="23">
-        <v>14</v>
-      </c>
-      <c r="G21" s="23">
-        <v>6</v>
-      </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.6</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr"/>
+      <c r="I21" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K21" s="23">
-        <v>6</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7.Wave.1</t>
+          <t>Encounter.7.Wave.1</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7</t>
-        </is>
-      </c>
-      <c r="C22" s="23">
-        <v>1</v>
-      </c>
-      <c r="D22" s="23">
-        <v>0</v>
-      </c>
-      <c r="E22" s="23">
-        <v>42</v>
-      </c>
-      <c r="F22" s="23">
-        <v>16</v>
-      </c>
-      <c r="G22" s="23">
-        <v>8</v>
-      </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.7</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr"/>
+      <c r="I22" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K22" s="23">
-        <v>7</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="L22" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7.Wave.2</t>
+          <t>Encounter.7.Wave.2</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7</t>
-        </is>
-      </c>
-      <c r="C23" s="23">
-        <v>2</v>
-      </c>
-      <c r="D23" s="23">
-        <v>10</v>
-      </c>
-      <c r="E23" s="23">
-        <v>40</v>
-      </c>
-      <c r="F23" s="23">
-        <v>16</v>
-      </c>
-      <c r="G23" s="23">
-        <v>6</v>
-      </c>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.7</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr"/>
+      <c r="I23" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K23" s="23">
-        <v>7</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7.Wave.3</t>
+          <t>Encounter.7.Wave.3</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.7</t>
-        </is>
-      </c>
-      <c r="C24" s="23">
-        <v>3</v>
-      </c>
-      <c r="D24" s="23">
-        <v>20</v>
-      </c>
-      <c r="E24" s="23">
-        <v>47</v>
-      </c>
-      <c r="F24" s="23">
-        <v>18</v>
-      </c>
-      <c r="G24" s="23">
-        <v>8</v>
-      </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.7</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr"/>
+      <c r="I24" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K24" s="23">
-        <v>7</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="L24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微《怪物》投放成长表</t>
+          <t>企微《怪物》投放成长表</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8.Wave.1</t>
+          <t>Encounter.8.Wave.1</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8</t>
-        </is>
-      </c>
-      <c r="C25" s="26">
-        <v>1</v>
-      </c>
-      <c r="D25" s="26">
-        <v>0</v>
-      </c>
-      <c r="E25" s="26">
-        <v>40</v>
-      </c>
-      <c r="F25" s="26">
-        <v>10</v>
-      </c>
-      <c r="G25" s="26">
-        <v>4</v>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_SHEEP</t>
-        </is>
-      </c>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>M_SHEEP</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K25" s="26">
-        <v>8</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K25" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="L25" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss在0秒刷新；40近战/10远程/4精英援军</t>
+          <t>Boss在0秒刷新；16近战/8远程/5精英援军</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8.Wave.2</t>
+          <t>Encounter.8.Wave.2</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8</t>
-        </is>
-      </c>
-      <c r="C26" s="26">
-        <v>2</v>
-      </c>
-      <c r="D26" s="26">
-        <v>10</v>
-      </c>
-      <c r="E26" s="26">
-        <v>30</v>
-      </c>
-      <c r="F26" s="26">
-        <v>10</v>
-      </c>
-      <c r="G26" s="26">
-        <v>5</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr"/>
+      <c r="I26" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="J26" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K26" s="26">
-        <v>8</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss关增援波</t>
+          <t>Boss关增援波</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8.Wave.3</t>
+          <t>Encounter.8.Wave.3</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounter.8</t>
-        </is>
-      </c>
-      <c r="C27" s="26">
-        <v>3</v>
-      </c>
-      <c r="D27" s="26">
-        <v>20</v>
-      </c>
-      <c r="E27" s="26">
-        <v>36</v>
-      </c>
-      <c r="F27" s="26">
-        <v>12</v>
-      </c>
-      <c r="G27" s="26">
-        <v>7</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Encounter.8</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr"/>
+      <c r="I27" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="J27" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">企微怪物表</t>
-        </is>
-      </c>
-      <c r="K27" s="26">
-        <v>8</v>
+          <t>怪物.xlsx</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boss关增援波</t>
-        </is>
-      </c>
-    </row>
+          <t>Boss关增援波</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <dataValidations count="2">
     <dataValidation sqref="B4:B27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblEncounters[Id]")</formula1>
@@ -2881,20 +3254,16 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.5" customWidth="1" min="1" max="1"/>
@@ -2919,6 +3288,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2989,171 +3359,195 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spawn.Melee</t>
+          <t>Spawn.Melee</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melee</t>
+          <t>Melee</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_SLIME</t>
-        </is>
-      </c>
-      <c r="D4" s="20">
-        <v>620</v>
-      </c>
-      <c r="E4" s="20">
-        <v>820</v>
-      </c>
-      <c r="F4" s="20">
-        <v>110</v>
-      </c>
-      <c r="G4" s="20">
-        <v>0.8</v>
+          <t>M_SLIME</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NormalAroundAnchor</t>
+          <t>NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicit</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Explicit</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="b">
+        <v>1</v>
       </c>
       <c r="K4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">刷怪规则</t>
-        </is>
-      </c>
-      <c r="L4" s="20">
-        <v>9</v>
+          <t>刷怪规则</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">近战出生参数</t>
+          <t>近战出生参数</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spawn.Ranged</t>
+          <t>Spawn.Ranged</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranged</t>
+          <t>Ranged</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_RABBIT</t>
-        </is>
-      </c>
-      <c r="D5" s="23">
-        <v>750</v>
-      </c>
-      <c r="E5" s="23">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="23">
-        <v>125</v>
-      </c>
-      <c r="G5" s="23">
-        <v>0.8</v>
+          <t>M_RABBIT</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NormalAroundAnchor</t>
+          <t>NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicit</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Explicit</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">刷怪规则</t>
-        </is>
-      </c>
-      <c r="L5" s="23">
-        <v>10</v>
+          <t>刷怪规则</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="M5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">远程出生参数</t>
+          <t>远程出生参数</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spawn.Elite</t>
+          <t>Spawn.Elite</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elite</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_FOX</t>
-        </is>
-      </c>
-      <c r="D6" s="23">
-        <v>700</v>
-      </c>
-      <c r="E6" s="23">
-        <v>900</v>
-      </c>
-      <c r="F6" s="23">
-        <v>200</v>
-      </c>
-      <c r="G6" s="23">
-        <v>1</v>
+          <t>M_FOX</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NormalAroundAnchor</t>
+          <t>NormalAroundAnchor</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicit</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true</t>
-        </is>
+          <t>Explicit</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">刷怪规则</t>
-        </is>
-      </c>
-      <c r="L6" s="23">
-        <v>11</v>
+          <t>刷怪规则</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">精英出生参数</t>
+          <t>精英出生参数</t>
         </is>
       </c>
     </row>
@@ -3173,17 +3567,25 @@
           <t>M_SLIME</t>
         </is>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>700</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>950</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>0.9</v>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
@@ -3195,18 +3597,18 @@
           <t>UseEnemyRole</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="J7" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="K7" s="26" t="inlineStr">
         <is>
           <t>刷怪规则</t>
         </is>
       </c>
-      <c r="L7" s="26" t="n">
-        <v>12</v>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="M7" s="27" t="inlineStr">
         <is>
@@ -3230,17 +3632,25 @@
           <t>M_SHEEP</t>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>700</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>950</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>220</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>0.9</v>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
@@ -3252,18 +3662,18 @@
           <t>Explicit</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="J8" s="26" t="b">
+        <v>1</v>
       </c>
       <c r="K8" s="26" t="inlineStr">
         <is>
           <t>刷怪规则</t>
         </is>
       </c>
-      <c r="L8" s="26" t="n">
-        <v>13</v>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="M8" s="27" t="inlineStr">
         <is>
@@ -3271,11 +3681,17 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <dataValidations count="5">
     <dataValidation sqref="B4:B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"Melee,Ranged,Elite,BossReinforcement,Boss"</formula1>
@@ -3293,20 +3709,16 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.25" customWidth="1" min="1" max="1"/>
@@ -3331,6 +3743,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3404,14 +3817,20 @@
           <t>SpawnPolicy.Default</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C4" s="29" t="n">
-        <v>400</v>
-      </c>
-      <c r="D4" s="29" t="n">
-        <v>250</v>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
         <is>
@@ -3433,21 +3852,23 @@
           <t>LatestEncounterE1</t>
         </is>
       </c>
-      <c r="I4" s="29" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" s="29" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="K4" s="29" t="inlineStr">
         <is>
           <t>刷怪规则</t>
         </is>
       </c>
-      <c r="L4" s="29" t="n">
-        <v>17</v>
+      <c r="L4" s="29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="M4" s="30" t="inlineStr">
         <is>
@@ -3455,11 +3876,17 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <dataValidations count="5">
     <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"MirrorInward"</formula1>
@@ -3477,10 +3904,6 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/Design/Data/ReEchoEncounterData.xlsx
+++ b/Design/Data/ReEchoEncounterData.xlsx
@@ -609,12 +609,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.5" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -899,17 +898,11 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="4">
     <dataValidation sqref="C4:C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"Level00"</formula1>
@@ -924,16 +917,20 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.13000106811523" customWidth="1" min="1" max="1"/>
@@ -963,7 +960,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1112,10 +1108,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="L4" s="20" t="n">
+        <v>500</v>
       </c>
       <c r="M4" s="20" t="b">
         <v>1</v>
@@ -1200,10 +1194,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="L5" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M5" s="23" t="b">
         <v>1</v>
@@ -1288,10 +1280,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="L6" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M6" s="23" t="b">
         <v>1</v>
@@ -1376,10 +1366,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="L7" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M7" s="23" t="b">
         <v>1</v>
@@ -1464,10 +1452,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="L8" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M8" s="23" t="b">
         <v>1</v>
@@ -1552,10 +1538,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="L9" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M9" s="23" t="b">
         <v>1</v>
@@ -1640,10 +1624,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="L10" s="23" t="n">
+        <v>500</v>
       </c>
       <c r="M10" s="23" t="b">
         <v>1</v>
@@ -1728,10 +1710,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="L11" s="26" t="n">
+        <v>500</v>
       </c>
       <c r="M11" s="26" t="b">
         <v>0</v>
@@ -1760,17 +1740,11 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="6">
     <dataValidation sqref="C4:C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblStages[Id]")</formula1>
@@ -1791,16 +1765,20 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.38000106811523" customWidth="1" min="1" max="1"/>
@@ -1824,7 +1802,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1908,20 +1885,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E4" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
       <c r="I4" s="20" t="b">
@@ -1964,20 +1935,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E5" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="23" t="b">
@@ -2020,20 +1985,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E6" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="23" t="inlineStr"/>
       <c r="I6" s="23" t="b">
@@ -2076,20 +2035,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E7" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="23" t="inlineStr"/>
       <c r="I7" s="23" t="b">
@@ -2132,20 +2085,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E8" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="23" t="inlineStr"/>
       <c r="I8" s="23" t="b">
@@ -2188,20 +2135,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H9" s="23" t="inlineStr"/>
       <c r="I9" s="23" t="b">
@@ -2244,20 +2185,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E10" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H10" s="23" t="inlineStr"/>
       <c r="I10" s="23" t="b">
@@ -2300,20 +2235,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E11" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H11" s="23" t="inlineStr"/>
       <c r="I11" s="23" t="b">
@@ -2356,20 +2285,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E12" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="23" t="inlineStr"/>
       <c r="I12" s="23" t="b">
@@ -2412,20 +2335,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="E13" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H13" s="23" t="inlineStr"/>
       <c r="I13" s="23" t="b">
@@ -2468,20 +2385,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E14" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="23" t="inlineStr"/>
       <c r="I14" s="23" t="b">
@@ -2524,20 +2435,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E15" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="23" t="inlineStr"/>
       <c r="I15" s="23" t="b">
@@ -2580,20 +2485,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="E16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="23" t="inlineStr"/>
       <c r="I16" s="23" t="b">
@@ -2636,20 +2535,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>90</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H17" s="23" t="inlineStr"/>
       <c r="I17" s="23" t="b">
@@ -2692,20 +2585,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H18" s="23" t="inlineStr"/>
       <c r="I18" s="23" t="b">
@@ -2748,20 +2635,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E19" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H19" s="23" t="inlineStr"/>
       <c r="I19" s="23" t="b">
@@ -2804,20 +2685,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E20" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H20" s="23" t="inlineStr"/>
       <c r="I20" s="23" t="b">
@@ -2860,20 +2735,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="E21" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="23" t="inlineStr"/>
       <c r="I21" s="23" t="b">
@@ -2916,20 +2785,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>90</v>
       </c>
       <c r="H22" s="23" t="inlineStr"/>
       <c r="I22" s="23" t="b">
@@ -2972,20 +2835,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="E23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>100</v>
       </c>
       <c r="H23" s="23" t="inlineStr"/>
       <c r="I23" s="23" t="b">
@@ -3028,20 +2885,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="23" t="n">
+        <v>90</v>
       </c>
       <c r="H24" s="23" t="inlineStr"/>
       <c r="I24" s="23" t="b">
@@ -3084,20 +2935,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F25" s="26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G25" s="26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="E25" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>40</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
@@ -3144,20 +2989,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F26" s="26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E26" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>40</v>
       </c>
       <c r="H26" s="26" t="inlineStr"/>
       <c r="I26" s="26" t="b">
@@ -3200,20 +3039,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="F27" s="26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="E27" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>40</v>
       </c>
       <c r="H27" s="26" t="inlineStr"/>
       <c r="I27" s="26" t="b">
@@ -3235,17 +3068,11 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="2">
     <dataValidation sqref="B4:B27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>INDIRECT("tblEncounters[Id]")</formula1>
@@ -3254,16 +3081,20 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.5" customWidth="1" min="1" max="1"/>
@@ -3288,7 +3119,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3681,17 +3511,11 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="5">
     <dataValidation sqref="B4:B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"Melee,Ranged,Elite,BossReinforcement,Boss"</formula1>
@@ -3709,16 +3533,20 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.25" customWidth="1" min="1" max="1"/>
@@ -3743,7 +3571,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3876,17 +3703,11 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
   <dataValidations count="5">
     <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list" errorStyle="stop">
       <formula1>"MirrorInward"</formula1>
@@ -3904,6 +3725,10 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
